--- a/backend/dados.xlsx
+++ b/backend/dados.xlsx
@@ -1,24 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26827"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Juliano\Desktop\supervisorio\backend\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7C34454A-F3EC-4322-94AC-79F318BDF518}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+  <fileVersion appName="Calc" lowestEdited="7"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5201F9F0-AC24-4BF8-B803-0F720ED6DD57}"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
+    <sheet name="Planilha1" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
   </extLst>
 </workbook>
@@ -27,38 +22,56 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
-    <t>status</t>
-  </si>
-  <si>
-    <t>pecas_inspecionadas</t>
-  </si>
-  <si>
-    <t>pecas_aprovadas</t>
-  </si>
-  <si>
-    <t>pecas_rejeitadas</t>
-  </si>
-  <si>
-    <t>taxa_rejeicao</t>
-  </si>
-  <si>
-    <t>Em operação</t>
-  </si>
-  <si>
-    <t>7.53</t>
+    <t xml:space="preserve">status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pecas_inspecionadas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pecas_aprovadas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pecas_rejeitadas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">taxa_rejeicao</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EM OPERAÇÃO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="General"/>
+  </numFmts>
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
     </font>
   </fonts>
   <fills count="2">
@@ -70,7 +83,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
@@ -78,40 +91,65 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="20">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+  <cellXfs count="3">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tema do Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -146,153 +184,55 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme>
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
                 <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
                 <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
                 <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
                 <a:lumMod val="102000"/>
                 <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
                 <a:lumMod val="100000"/>
                 <a:shade val="100000"/>
               </a:schemeClr>
@@ -300,33 +240,24 @@
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
                 <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
@@ -339,13 +270,7 @@
           <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
@@ -355,15 +280,13 @@
         <a:solidFill>
           <a:schemeClr val="phClr">
             <a:tint val="95000"/>
-            <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="93000"/>
-                <a:satMod val="150000"/>
                 <a:shade val="98000"/>
                 <a:lumMod val="102000"/>
               </a:schemeClr>
@@ -371,7 +294,6 @@
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:tint val="98000"/>
-                <a:satMod val="130000"/>
                 <a:shade val="90000"/>
                 <a:lumMod val="103000"/>
               </a:schemeClr>
@@ -379,72 +301,74 @@
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="63000"/>
-                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B4FC01B-1137-46F9-883D-C1B7FBBB86E5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="18.42578125" customWidth="1"/>
-    <col min="2" max="2" width="19.28515625" customWidth="1"/>
-    <col min="3" max="3" width="17" customWidth="1"/>
-    <col min="4" max="4" width="18.85546875" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="18.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="19.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="18.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="14.86"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="1" t="n">
         <v>9842</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="1" t="n">
         <v>9102</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="1" t="n">
         <v>740</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="1" t="s">
         <v>6</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.511805555555556" right="0.511805555555556" top="0.7875" bottom="0.7875" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/backend/dados.xlsx
+++ b/backend/dados.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t xml:space="preserve">status</t>
   </si>
@@ -35,6 +35,18 @@
   </si>
   <si>
     <t xml:space="preserve">taxa_rejeicao</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inicio_parada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tempo_parado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">media_paradas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">total_paradas</t>
   </si>
   <si>
     <t xml:space="preserve">EM OPERAÇÃO</t>
@@ -47,8 +59,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="hh:mm:ss"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -116,7 +129,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -127,6 +140,14 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -318,7 +339,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="18.42"/>
@@ -326,6 +347,10 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="17"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="18.86"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="14.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="11.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="12.9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="13.76"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="13.44"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -344,10 +369,22 @@
       <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
+      <c r="F1" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="0" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1" t="n">
         <v>9842</v>
@@ -359,7 +396,19 @@
         <v>740</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>6</v>
+        <v>10</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>0.60125</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>0.00454861111111111</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>0.00435185185185185</v>
+      </c>
+      <c r="I2" s="4" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/backend/dados.xlsx
+++ b/backend/dados.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
   <si>
     <t xml:space="preserve">status</t>
   </si>
@@ -49,19 +49,119 @@
     <t xml:space="preserve">total_paradas</t>
   </si>
   <si>
+    <t xml:space="preserve">status_garrafa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">camera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">confianca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trinca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mancha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sujeira</t>
+  </si>
+  <si>
+    <t xml:space="preserve">risco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">outro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">marca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sku</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lote</t>
+  </si>
+  <si>
+    <t xml:space="preserve">envase</t>
+  </si>
+  <si>
+    <t xml:space="preserve">linha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">velocidade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eficiencia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">disponibilidade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">qualidade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">oee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mtbf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mttr</t>
+  </si>
+  <si>
     <t xml:space="preserve">EM OPERAÇÃO</t>
   </si>
   <si>
     <t xml:space="preserve">7.53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Presença de solda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C03: Esquerda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">185 (42,8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92 (21,1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64 (14,7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51 (11,8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31 (7,0%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12 (2,9%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMSTEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMSTEL 800ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L240517B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linha 9</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="hh:mm:ss"/>
+    <numFmt numFmtId="166" formatCode="dd/mm/yy\ hh:mm"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -129,7 +229,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -142,12 +242,24 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -339,18 +451,32 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:AD2"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="18.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="17.23"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="19.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="17"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="18.86"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="14.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="11.27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="12.9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="13.76"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="13.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="11.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="12.9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="13.75"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="13.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="15.07"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="12.47"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="10.95"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="9.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="10.62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="9.97"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="10.51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="10.08"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="12.9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="17.02"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="0" width="11.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="0" width="9.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="0" width="14.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="29" style="0" width="11.05"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -369,22 +495,85 @@
       <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" s="0" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="B2" s="1" t="n">
         <v>9842</v>
@@ -396,7 +585,7 @@
         <v>740</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>0.60125</v>
@@ -409,6 +598,69 @@
       </c>
       <c r="I2" s="4" t="n">
         <v>5</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="L2" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="S2" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="T2" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="U2" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="V2" s="6" t="n">
+        <v>45794.34375</v>
+      </c>
+      <c r="W2" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="X2" s="0" t="n">
+        <v>30000</v>
+      </c>
+      <c r="Y2" s="0" t="n">
+        <v>91.3</v>
+      </c>
+      <c r="Z2" s="0" t="n">
+        <v>86.8</v>
+      </c>
+      <c r="AA2" s="0" t="n">
+        <v>92.6</v>
+      </c>
+      <c r="AB2" s="0" t="n">
+        <v>72.9</v>
+      </c>
+      <c r="AC2" s="7" t="n">
+        <v>0.117210648148148</v>
+      </c>
+      <c r="AD2" s="7" t="n">
+        <v>0.00436342592592593</v>
       </c>
     </row>
   </sheetData>

--- a/backend/dados.xlsx
+++ b/backend/dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aluno.alagoinhas\supervisorio\backend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B79053A0-54BE-4FF4-BF95-1F064F7297EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E35A29EA-E739-4FF7-97C5-4EB052A1023A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -206,46 +206,46 @@
     <t>51 (11,8%)</t>
   </si>
   <si>
+    <t>12 (2,9%)</t>
+  </si>
+  <si>
+    <t>Linha 9</t>
+  </si>
+  <si>
+    <t>Garrafa trincada</t>
+  </si>
+  <si>
+    <t>Trinca no corpo</t>
+  </si>
+  <si>
+    <t>Garrafa com mancha</t>
+  </si>
+  <si>
+    <t>Soda cáustica</t>
+  </si>
+  <si>
+    <t>Garrafa suja</t>
+  </si>
+  <si>
+    <t>OK</t>
+  </si>
+  <si>
+    <t>Câmera: C03 - Lateral</t>
+  </si>
+  <si>
+    <t>L240517A</t>
+  </si>
+  <si>
+    <t>Confiabildade: 94%</t>
+  </si>
+  <si>
+    <t>AMSTEL</t>
+  </si>
+  <si>
+    <t>AMSTEL 600ml</t>
+  </si>
+  <si>
     <t>31 (7,0%)</t>
-  </si>
-  <si>
-    <t>12 (2,9%)</t>
-  </si>
-  <si>
-    <t>Linha 9</t>
-  </si>
-  <si>
-    <t>Garrafa trincada</t>
-  </si>
-  <si>
-    <t>Trinca no corpo</t>
-  </si>
-  <si>
-    <t>Garrafa com mancha</t>
-  </si>
-  <si>
-    <t>Soda cáustica</t>
-  </si>
-  <si>
-    <t>Garrafa suja</t>
-  </si>
-  <si>
-    <t>OK</t>
-  </si>
-  <si>
-    <t>Câmera: C03 - Lateral</t>
-  </si>
-  <si>
-    <t>SCHIN</t>
-  </si>
-  <si>
-    <t>SCHIN 600ml</t>
-  </si>
-  <si>
-    <t>L240517A</t>
-  </si>
-  <si>
-    <t>Confiabildade: 94%</t>
   </si>
 </sst>
 </file>
@@ -672,10 +672,10 @@
         <v>56</v>
       </c>
       <c r="K2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L2" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="M2" t="s">
         <v>57</v>
@@ -690,40 +690,40 @@
         <v>60</v>
       </c>
       <c r="Q2" t="s">
+        <v>74</v>
+      </c>
+      <c r="R2" t="s">
         <v>61</v>
       </c>
-      <c r="R2" t="s">
-        <v>62</v>
-      </c>
       <c r="S2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="T2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="U2" s="3" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="V2" s="4">
         <v>45794.34375</v>
       </c>
       <c r="W2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="X2">
         <v>24000</v>
       </c>
       <c r="Y2">
-        <v>91.2</v>
+        <v>70</v>
       </c>
       <c r="Z2">
-        <v>86.7</v>
+        <v>81.7</v>
       </c>
       <c r="AA2">
         <v>60</v>
       </c>
       <c r="AB2">
-        <v>72.8</v>
+        <v>63.8</v>
       </c>
       <c r="AC2" s="5">
         <v>0.11686342592592593</v>
@@ -735,10 +735,10 @@
         <v>0.5223726851851852</v>
       </c>
       <c r="AF2" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG2" t="s">
         <v>64</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>65</v>
       </c>
       <c r="AH2">
         <v>6</v>
@@ -750,10 +750,10 @@
         <v>35.4</v>
       </c>
       <c r="AK2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="AL2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:38" x14ac:dyDescent="0.25">
@@ -761,10 +761,10 @@
         <v>0.60561342592592593</v>
       </c>
       <c r="AF3" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG3" t="s">
         <v>64</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="4" spans="1:38" x14ac:dyDescent="0.25">
@@ -772,10 +772,10 @@
         <v>0.60553240740740744</v>
       </c>
       <c r="AF4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AG4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:38" x14ac:dyDescent="0.25">
@@ -783,10 +783,10 @@
         <v>0.60540509259259256</v>
       </c>
       <c r="AF5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="AG5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:38" x14ac:dyDescent="0.25">
@@ -794,10 +794,10 @@
         <v>0.59855324074074079</v>
       </c>
       <c r="AF6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AG6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>

--- a/backend/dados.xlsx
+++ b/backend/dados.xlsx
@@ -149,19 +149,19 @@
     <t xml:space="preserve">Câmera: C03 - Lateral</t>
   </si>
   <si>
-    <t xml:space="preserve">Confiabildade: 94%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">185 (42,8%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92 (21,1%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94 (14,7%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51 (11,8%)</t>
+    <t xml:space="preserve">Confiabildade: 92%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">191 (42,8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96 (21,1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98 (14,7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53 (11,8%)</t>
   </si>
   <si>
     <t xml:space="preserve">31 (7,0%)</t>
@@ -170,13 +170,14 @@
     <t xml:space="preserve">12 (2,9%)</t>
   </si>
   <si>
-    <t xml:space="preserve">AMSTEL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMSTEL 600ml</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L240517A</t>
+    <t xml:space="preserve">SCHIN
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCHIN 600ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L240519H</t>
   </si>
   <si>
     <t xml:space="preserve">Linha 9</t>
@@ -359,7 +360,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -377,6 +378,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -732,28 +737,28 @@
         <v>38</v>
       </c>
       <c r="B2" s="1" t="n">
-        <v>9842</v>
+        <v>5231</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>9102</v>
+        <v>2354</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>740</v>
+        <v>700</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>39</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.60125</v>
+        <v>0.642916666666667</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.00453703703703704</v>
+        <v>0.00523148148148148</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>0.00434027777777778</v>
+        <v>0.00503472222222222</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>40</v>
@@ -782,7 +787,7 @@
       <c r="R2" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="S2" s="5" t="s">
         <v>49</v>
       </c>
       <c r="T2" s="1" t="s">
@@ -791,34 +796,34 @@
       <c r="U2" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="V2" s="5" t="n">
-        <v>45794.34375</v>
+      <c r="V2" s="6" t="n">
+        <v>46193.34375</v>
       </c>
       <c r="W2" s="1" t="s">
         <v>52</v>
       </c>
       <c r="X2" s="1" t="n">
-        <v>24000</v>
+        <v>34000</v>
       </c>
       <c r="Y2" s="1" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="Z2" s="1" t="n">
         <v>81.7</v>
       </c>
       <c r="AA2" s="1" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="AB2" s="1" t="n">
-        <v>63.8</v>
-      </c>
-      <c r="AC2" s="6" t="n">
+        <v>68.8</v>
+      </c>
+      <c r="AC2" s="7" t="n">
         <v>0.116863425925926</v>
       </c>
-      <c r="AD2" s="6" t="n">
+      <c r="AD2" s="7" t="n">
         <v>0.00434027777777778</v>
       </c>
-      <c r="AE2" s="6" t="n">
+      <c r="AE2" s="7" t="n">
         <v>0.522372685185185</v>
       </c>
       <c r="AF2" s="1" t="s">
@@ -828,13 +833,13 @@
         <v>54</v>
       </c>
       <c r="AH2" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AI2" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AJ2" s="1" t="n">
-        <v>35.4</v>
+        <v>35.6</v>
       </c>
       <c r="AK2" s="1" t="s">
         <v>55</v>
@@ -844,7 +849,7 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AE3" s="6" t="n">
+      <c r="AE3" s="7" t="n">
         <v>0.605613425925926</v>
       </c>
       <c r="AF3" s="1" t="s">
@@ -855,7 +860,7 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AE4" s="6" t="n">
+      <c r="AE4" s="7" t="n">
         <v>0.605532407407407</v>
       </c>
       <c r="AF4" s="1" t="s">
@@ -866,7 +871,7 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AE5" s="6" t="n">
+      <c r="AE5" s="7" t="n">
         <v>0.605405092592593</v>
       </c>
       <c r="AF5" s="1" t="s">
@@ -877,7 +882,7 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AE6" s="6" t="n">
+      <c r="AE6" s="7" t="n">
         <v>0.598553240740741</v>
       </c>
       <c r="AF6" s="1" t="s">
